--- a/reference.xlsx
+++ b/reference.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$C$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$C$186</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="366">
   <si>
     <t>ND</t>
   </si>
@@ -35,562 +35,52 @@
     <t>Client</t>
   </si>
   <si>
-    <t>2723466772</t>
-  </si>
-  <si>
-    <t>PRESIDENCE DE LA REPUBLIQUE</t>
-  </si>
-  <si>
-    <t>11/11/2025</t>
-  </si>
-  <si>
-    <t>2723535999</t>
-  </si>
-  <si>
-    <t>STE DREAM COSMETICS</t>
-  </si>
-  <si>
-    <t>SYTHD220230</t>
-  </si>
-  <si>
-    <t>STE BRASSIVOIRE</t>
-  </si>
-  <si>
-    <t>2721710780</t>
-  </si>
-  <si>
-    <t>STE AGRO INDUSTRIE DE COTE D IVOIRE</t>
-  </si>
-  <si>
     <t>10/05/2026</t>
   </si>
   <si>
-    <t>BUVPN240154</t>
-  </si>
-  <si>
     <t>SGCI</t>
   </si>
   <si>
-    <t>SYTHD250075</t>
-  </si>
-  <si>
-    <t>STE STE LG ELECTRONICS AFRICA LOGISTICS FZE</t>
-  </si>
-  <si>
-    <t>2722501714</t>
-  </si>
-  <si>
-    <t>ASSOC COMMISSION D ACCES A L INFORMATION D INTERETS P ET AUX DOCS</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>2722414461</t>
-  </si>
-  <si>
-    <t>STE CENTRE NATIONAL DE DOCUMENTATION JURIDIQUE</t>
-  </si>
-  <si>
-    <t>2722548600</t>
-  </si>
-  <si>
-    <t>FER</t>
-  </si>
-  <si>
-    <t>BUVPN230135</t>
-  </si>
-  <si>
-    <t>ORG AGENCE DE GESTION DES ROUTES</t>
-  </si>
-  <si>
-    <t>BUVPN150352</t>
-  </si>
-  <si>
     <t>ECOBANK</t>
   </si>
   <si>
-    <t>2722549405</t>
-  </si>
-  <si>
-    <t>STE ONPOINT CONSULTING GROUP COTE D IVOIRE</t>
-  </si>
-  <si>
-    <t>2722507830</t>
-  </si>
-  <si>
-    <t>STE FLASH VEHICLES</t>
-  </si>
-  <si>
-    <t>BUVPN160156</t>
-  </si>
-  <si>
-    <t>STE BANQUE REGIONALE DE MARCHES COTE D IVOIRE</t>
-  </si>
-  <si>
-    <t>2721750600</t>
-  </si>
-  <si>
-    <t>STE SPIRAL SARL</t>
-  </si>
-  <si>
     <t>20/05/2026</t>
   </si>
   <si>
-    <t>BUVPN170285</t>
-  </si>
-  <si>
     <t>BOLLORE</t>
   </si>
   <si>
-    <t>SYTHD190019</t>
-  </si>
-  <si>
     <t>LOTERIE NATIONALE DE CI LONACI</t>
   </si>
   <si>
-    <t>BUVPN220151</t>
-  </si>
-  <si>
-    <t>NSIA</t>
-  </si>
-  <si>
-    <t>BUVPN150085</t>
-  </si>
-  <si>
-    <t>BOA</t>
-  </si>
-  <si>
-    <t>VPNLL050192</t>
-  </si>
-  <si>
     <t>DOUANES</t>
   </si>
   <si>
-    <t>2721233000</t>
-  </si>
-  <si>
-    <t>GROUPEMENT DES SERVICES EAU ET ELECTRICITE CIE SODECI ET GS2E</t>
-  </si>
-  <si>
-    <t>BUVPN230216</t>
-  </si>
-  <si>
-    <t>SYTHD160040</t>
-  </si>
-  <si>
-    <t>STE MEDLOG</t>
-  </si>
-  <si>
-    <t>VPNLL060010</t>
-  </si>
-  <si>
-    <t>SYTHD180074</t>
-  </si>
-  <si>
-    <t>STE BERNABE CI KM4</t>
-  </si>
-  <si>
-    <t>2721235900</t>
-  </si>
-  <si>
-    <t>STE CMA CGM COTE D IVOIRE</t>
-  </si>
-  <si>
-    <t>2721750900</t>
-  </si>
-  <si>
-    <t>STE CROWN SIEM</t>
-  </si>
-  <si>
-    <t>2721239200</t>
-  </si>
-  <si>
-    <t>BUVPN220122</t>
-  </si>
-  <si>
-    <t>2721355723</t>
-  </si>
-  <si>
-    <t>ORG CENTRE NATIONAL DE TRANSFUSION SANGUINE</t>
-  </si>
-  <si>
-    <t>2722598310</t>
-  </si>
-  <si>
-    <t>MIN MINISTERE DE LA FAMILLE</t>
-  </si>
-  <si>
-    <t>17/02/2026</t>
-  </si>
-  <si>
-    <t>2722228640</t>
-  </si>
-  <si>
-    <t>STE REGUS PLEIN CIEL BUSINESS CENTER</t>
-  </si>
-  <si>
     <t>18/02/2026</t>
   </si>
   <si>
-    <t>2722509600</t>
-  </si>
-  <si>
-    <t>ASSOC MUPEMENET CI</t>
-  </si>
-  <si>
-    <t>BUVPN210191</t>
-  </si>
-  <si>
     <t>TRESOR</t>
   </si>
   <si>
-    <t>BUVPN240030</t>
-  </si>
-  <si>
-    <t>STE ASSUREURS CONSEILS COTE D IVOIRE</t>
-  </si>
-  <si>
-    <t>SYTHD200196</t>
-  </si>
-  <si>
-    <t>STE GRANT THORNTON AUDIT COTE D IVOIRE SAS</t>
-  </si>
-  <si>
-    <t>2722417110</t>
-  </si>
-  <si>
-    <t>STE COMPAGNIE AFRICAINE DE CREDIT</t>
-  </si>
-  <si>
-    <t>SYTHD240333</t>
-  </si>
-  <si>
-    <t>VPNLL110030</t>
-  </si>
-  <si>
-    <t>ETS BANQUE SAHELO SAHARIENNE POUR L INVESTISSEMENT ET LE COMMERCE EN COTE D IVOIRE</t>
-  </si>
-  <si>
-    <t>SYTHD120066</t>
-  </si>
-  <si>
-    <t>STE SOCIETE DE TRANSPORT ABIDJANAIS</t>
-  </si>
-  <si>
-    <t>28/11/2025</t>
-  </si>
-  <si>
-    <t>BUVPN190213</t>
-  </si>
-  <si>
-    <t>BUVPN210064</t>
-  </si>
-  <si>
-    <t>2721757100</t>
-  </si>
-  <si>
-    <t>2721221895</t>
-  </si>
-  <si>
-    <t>STE SOCIETE INTERNATIONALE DE LOGSTIQUE SHIPPING</t>
-  </si>
-  <si>
-    <t>22/02/2026</t>
-  </si>
-  <si>
-    <t>BUVPN200057</t>
-  </si>
-  <si>
-    <t>STE NATIONALE D OPERATION PETROLIERES DE COTE D IVOIRE</t>
-  </si>
-  <si>
-    <t>2721283888</t>
-  </si>
-  <si>
-    <t>STE TEDIS PHARMA COTE D IVOIRE</t>
-  </si>
-  <si>
-    <t>2721220400</t>
-  </si>
-  <si>
-    <t>BUVPN230241</t>
-  </si>
-  <si>
-    <t>STE AFRICA GLOBAL LOGISTICS</t>
-  </si>
-  <si>
-    <t>VPNLL070046</t>
-  </si>
-  <si>
-    <t>VPNLL060188</t>
-  </si>
-  <si>
-    <t>SYTHD230263</t>
-  </si>
-  <si>
-    <t>STE ROMEU</t>
-  </si>
-  <si>
-    <t>2721599555</t>
-  </si>
-  <si>
-    <t>STE KOIRA MULTI INDUSTRIES</t>
-  </si>
-  <si>
-    <t>SYTHD250223</t>
-  </si>
-  <si>
-    <t>SIFCOM</t>
-  </si>
-  <si>
-    <t>BUVPN200094</t>
-  </si>
-  <si>
-    <t>BUVPN200080</t>
-  </si>
-  <si>
     <t>STE CORIS BANK INTERNATIONAL</t>
   </si>
   <si>
-    <t>SYTHD110016</t>
-  </si>
-  <si>
-    <t>STE SIFCOM</t>
-  </si>
-  <si>
-    <t>BUVPN230234</t>
-  </si>
-  <si>
-    <t>2721245007</t>
-  </si>
-  <si>
-    <t>CHAMBRE DE COMMERCE ET D INDUSTRIE DE COTE D IVOIRE D IVOIRE</t>
-  </si>
-  <si>
-    <t>SYTHD230205</t>
-  </si>
-  <si>
-    <t>ETS CHAMBRE DE COMMERCE ET D INDUSTRIE DE COTE D IVOIRE D IVOIRE</t>
-  </si>
-  <si>
-    <t>SYTHD240155</t>
-  </si>
-  <si>
-    <t>STE ORANGE COTE D IVOIRE S A</t>
-  </si>
-  <si>
-    <t>BUVPN150580</t>
-  </si>
-  <si>
-    <t>BUVPN180031</t>
-  </si>
-  <si>
-    <t>BUVPN230068</t>
-  </si>
-  <si>
-    <t>VPNLL060013</t>
-  </si>
-  <si>
-    <t>2721755835</t>
-  </si>
-  <si>
-    <t>BUVPN220259</t>
-  </si>
-  <si>
-    <t>2720255050</t>
-  </si>
-  <si>
-    <t>STE CYRIAN INTERNATIONAL</t>
-  </si>
-  <si>
     <t>06/03/2026</t>
   </si>
   <si>
-    <t>2720278880</t>
-  </si>
-  <si>
-    <t>MAJORIS FINANCIAL GROUP</t>
-  </si>
-  <si>
-    <t>2720307650</t>
-  </si>
-  <si>
-    <t>COMPAGNIE IVOIRIENNE DE PRODUCTION D ELECTRICITE</t>
-  </si>
-  <si>
-    <t>BUVPN220261</t>
-  </si>
-  <si>
-    <t>STE CITIBANK COTE D IVOIRE SA</t>
-  </si>
-  <si>
-    <t>2720229418</t>
-  </si>
-  <si>
-    <t>ETS CABINET DE MAITRE ZEHOURI</t>
-  </si>
-  <si>
-    <t>SYTHD240290</t>
-  </si>
-  <si>
-    <t>STE SEALOGIS PROJETS COTE D IVOIRE</t>
-  </si>
-  <si>
-    <t>SYTHD230229</t>
-  </si>
-  <si>
-    <t>STE DEPOSITAIRE CENTRAL BANQUE DE REGLEMENT</t>
-  </si>
-  <si>
-    <t>2720332960</t>
-  </si>
-  <si>
-    <t>SYTHD250248</t>
-  </si>
-  <si>
-    <t>SOCIETE DE COMMERCIALISATION DE CAFE CACAO</t>
-  </si>
-  <si>
     <t>14/05/2026</t>
   </si>
   <si>
-    <t>2721221838</t>
-  </si>
-  <si>
-    <t>STE COLIMEX IVORY</t>
-  </si>
-  <si>
-    <t>SYTHD240087</t>
-  </si>
-  <si>
-    <t>STE ALTERA INFRASTRUCTURE VOYAGEUR AS</t>
-  </si>
-  <si>
-    <t>BUVPN250038</t>
-  </si>
-  <si>
     <t>SIB</t>
   </si>
   <si>
-    <t>BUVPN180045</t>
-  </si>
-  <si>
-    <t>2721258305</t>
-  </si>
-  <si>
-    <t>STE RADIODIFFUSION TELEVISION IVOIRIENNE</t>
-  </si>
-  <si>
-    <t>2721756925</t>
-  </si>
-  <si>
-    <t>STE OCEAN NETWORK EXPRESS IVOIRY COAST</t>
-  </si>
-  <si>
-    <t>2721358883</t>
-  </si>
-  <si>
-    <t>STE TRANSIT CENTER</t>
-  </si>
-  <si>
-    <t>VPNLL110089</t>
-  </si>
-  <si>
-    <t>2721222221</t>
-  </si>
-  <si>
-    <t>STE SOGENA COTE D IVOIRE</t>
-  </si>
-  <si>
-    <t>BUVPN230256</t>
-  </si>
-  <si>
-    <t>13/11/2025</t>
-  </si>
-  <si>
-    <t>2721212250</t>
-  </si>
-  <si>
-    <t>STE GRAPHICOLOR</t>
-  </si>
-  <si>
-    <t>BUVPN220282</t>
-  </si>
-  <si>
-    <t>2721216370</t>
-  </si>
-  <si>
-    <t>TECTRA</t>
-  </si>
-  <si>
-    <t>SYTHD140199</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>2721751480</t>
-  </si>
-  <si>
-    <t>STE GRAFICA IVOIRE</t>
-  </si>
-  <si>
-    <t>2721223232</t>
-  </si>
-  <si>
-    <t>SOCIETE IVOIRIENNE DE PROMOTION DE SUPERMARCHES</t>
-  </si>
-  <si>
-    <t>BUVPN170101</t>
-  </si>
-  <si>
     <t>DGI</t>
   </si>
   <si>
-    <t>VPNLL060048</t>
-  </si>
-  <si>
-    <t>BUVPN230214</t>
-  </si>
-  <si>
-    <t>2721251587</t>
-  </si>
-  <si>
     <t>STE GMT SHIPPING CI SA</t>
   </si>
   <si>
-    <t>SYTHD250014</t>
-  </si>
-  <si>
-    <t>LE CLIENT STE UNITED CAPITAL ASSET MANAGEMENT WEST AFRICA LIMITED</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>SYTHD230248</t>
-  </si>
-  <si>
-    <t>STE TRIDEM PHARMA AFRIQUE FRANCOPHONE</t>
-  </si>
-  <si>
-    <t>2722228910</t>
-  </si>
-  <si>
-    <t>STE UNITED CAPITAL ASSET MANAGEMENT WEST AFRICA LIMITED</t>
-  </si>
-  <si>
-    <t>2723536464</t>
-  </si>
-  <si>
-    <t>STE INDUSTRIELLE DE PRODUITS PLASTIQUES ET CHIMIQUES</t>
-  </si>
-  <si>
     <t>12/04/2025</t>
-  </si>
-  <si>
-    <t>BUVPN240168</t>
   </si>
   <si>
     <t>STE BGFIBANK</t>
@@ -1706,7 +1196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1731,9 +1221,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2048,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C286"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="1"/>
@@ -2064,3153 +1551,2053 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>534</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>64</v>
+        <v>85</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>83</v>
+        <v>95</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="10">
-        <v>45989</v>
+        <v>102</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>89</v>
+        <v>107</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>45</v>
+        <v>143</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>45</v>
+        <v>143</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>137</v>
+        <v>3</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>141</v>
+        <v>160</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>147</v>
+        <v>54</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>159</v>
+        <v>8</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>168</v>
+        <v>8</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C93" s="9" t="s">
-        <v>159</v>
+        <v>188</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>186</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>45</v>
+        <v>214</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>141</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>141</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>210</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>213</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>215</v>
+        <v>4</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>213</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>213</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>213</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>213</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>45</v>
+        <v>233</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>45</v>
+        <v>243</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>235</v>
+        <v>8</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>243</v>
+        <v>160</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>39</v>
+        <v>261</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>261</v>
+        <v>8</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>265</v>
+        <v>149</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>268</v>
+        <v>8</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>266</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>266</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>266</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>125</v>
+        <v>285</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>125</v>
+        <v>285</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>125</v>
+        <v>285</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>125</v>
+        <v>285</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>125</v>
+        <v>285</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>125</v>
+        <v>295</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>71</v>
+        <v>297</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>125</v>
+        <v>298</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>71</v>
+        <v>300</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>125</v>
+        <v>255</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>125</v>
+        <v>255</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>71</v>
+        <v>304</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>125</v>
+        <v>255</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>125</v>
+        <v>307</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>293</v>
+        <v>264</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>301</v>
+        <v>102</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>302</v>
+        <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>304</v>
+        <v>11</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>310</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>176</v>
+        <v>327</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>310</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>310</v>
+        <v>40</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>125</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>125</v>
+      <c r="A169" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C169" s="3">
+        <v>45992</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>125</v>
+      <c r="A170" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C170" s="3">
+        <v>45994</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>125</v>
+      <c r="A171" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C171" s="3">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C172" s="3">
+        <v>46000</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>125</v>
+      <c r="A173" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C173" s="3">
+        <v>46007</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>125</v>
+      <c r="A174" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C174" s="3">
+        <v>46008</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="C176" s="9" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>125</v>
+      <c r="A175" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C175" s="3">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C176" s="3">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C177" s="3">
+        <v>46010</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C178" s="3">
+        <v>46032</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>125</v>
+      <c r="A179" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C179" s="7">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C180" s="3">
+        <v>46099</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>125</v>
+      <c r="A181" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C181" s="3">
+        <v>46115</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>339</v>
+      <c r="A182" s="6">
+        <v>2721247429</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C182" s="7">
+        <v>46139</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>339</v>
+      <c r="A183" s="6">
+        <v>2721255054</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C183" s="7">
+        <v>46139</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>339</v>
+      <c r="A184" s="6">
+        <v>2721273128</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C184" s="7">
+        <v>46139</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>339</v>
+      <c r="A185" s="6">
+        <v>2721219191</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C185" s="7">
+        <v>46147</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C189" s="9" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="B191" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="B192" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="C194" s="5" t="s">
+      <c r="A186" s="6" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="5" t="s">
+      <c r="B186" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="B195" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="5" t="s">
+      <c r="C186" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="B196" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="B202" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C202" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B203" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="B205" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="B206" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="B208" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="B209" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="B210" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="C210" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="B211" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="B212" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="C212" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="B213" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="B214" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C214" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="B215" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="B216" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="C216" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="B217" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="C217" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="B218" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="C218" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="B219" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B220" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C220" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="B221" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="C221" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="B222" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="B223" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="B224" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="B225" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="B226" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="C226" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="B227" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="B228" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="C228" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="B229" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="B230" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="B232" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="B233" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="B234" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B235" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="B236" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="C236" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="B237" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C237" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="B238" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C238" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="B239" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B240" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="B241" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="B242" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="C242" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="B243" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="B244" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C244" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="B245" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="B246" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="C246" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B247" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="C247" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="B248" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="C248" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="B249" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="B250" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="C250" s="5" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="B251" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="B252" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="B253" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="B254" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="C254" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="B255" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="B256" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="C256" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="B257" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="B258" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C258" s="5" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="B259" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C259" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="B260" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="B261" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="B262" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="C262" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="B263" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="B264" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="C264" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="B265" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="B266" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="C266" s="5" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="B268" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="C268" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="C269" s="3">
-        <v>45992</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C270" s="3">
-        <v>45994</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C271" s="3">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A272" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="B272" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C272" s="3">
-        <v>46000</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C273" s="3">
-        <v>46007</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="C274" s="3">
-        <v>46008</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="C275" s="3">
-        <v>46008</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A276" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="B276" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="C276" s="3">
-        <v>46008</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A277" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="B277" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="C277" s="3">
-        <v>46010</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A278" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="B278" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="C278" s="3">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="B279" s="6" t="s">
-        <v>520</v>
-      </c>
-      <c r="C279" s="7">
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A280" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B280" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="C280" s="3">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C281" s="3">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" s="6">
-        <v>2721247429</v>
-      </c>
-      <c r="B282" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="C282" s="7">
-        <v>46139</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" s="6">
-        <v>2721255054</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>528</v>
-      </c>
-      <c r="C283" s="7">
-        <v>46139</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" s="6">
-        <v>2721273128</v>
-      </c>
-      <c r="B284" s="6" t="s">
-        <v>529</v>
-      </c>
-      <c r="C284" s="7">
-        <v>46139</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" s="6">
-        <v>2721219191</v>
-      </c>
-      <c r="B285" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="C285" s="7">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="B286" s="6" t="s">
-        <v>532</v>
-      </c>
-      <c r="C286" s="8" t="s">
-        <v>533</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C286"/>
-  <conditionalFormatting sqref="A283:A286 A269:A280">
+  <autoFilter ref="A1:C186"/>
+  <conditionalFormatting sqref="A183:A186 A169:A180">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A281:A282">
+  <conditionalFormatting sqref="A181:A182">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reference.xlsx
+++ b/reference.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$C$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$C$286</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="536">
   <si>
     <t>ND</t>
   </si>
@@ -35,52 +35,562 @@
     <t>Client</t>
   </si>
   <si>
+    <t>2723466772</t>
+  </si>
+  <si>
+    <t>PRESIDENCE DE LA REPUBLIQUE</t>
+  </si>
+  <si>
+    <t>11/11/2025</t>
+  </si>
+  <si>
+    <t>2723535999</t>
+  </si>
+  <si>
+    <t>STE DREAM COSMETICS</t>
+  </si>
+  <si>
+    <t>SYTHD220230</t>
+  </si>
+  <si>
+    <t>STE BRASSIVOIRE</t>
+  </si>
+  <si>
+    <t>2721710780</t>
+  </si>
+  <si>
+    <t>STE AGRO INDUSTRIE DE COTE D IVOIRE</t>
+  </si>
+  <si>
     <t>10/05/2026</t>
   </si>
   <si>
+    <t>BUVPN240154</t>
+  </si>
+  <si>
     <t>SGCI</t>
   </si>
   <si>
+    <t>SYTHD250075</t>
+  </si>
+  <si>
+    <t>STE STE LG ELECTRONICS AFRICA LOGISTICS FZE</t>
+  </si>
+  <si>
+    <t>2722501714</t>
+  </si>
+  <si>
+    <t>ASSOC COMMISSION D ACCES A L INFORMATION D INTERETS P ET AUX DOCS</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>2722414461</t>
+  </si>
+  <si>
+    <t>STE CENTRE NATIONAL DE DOCUMENTATION JURIDIQUE</t>
+  </si>
+  <si>
+    <t>2722548600</t>
+  </si>
+  <si>
+    <t>FER</t>
+  </si>
+  <si>
+    <t>BUVPN230135</t>
+  </si>
+  <si>
+    <t>ORG AGENCE DE GESTION DES ROUTES</t>
+  </si>
+  <si>
+    <t>BUVPN150352</t>
+  </si>
+  <si>
     <t>ECOBANK</t>
   </si>
   <si>
+    <t>2722549405</t>
+  </si>
+  <si>
+    <t>STE ONPOINT CONSULTING GROUP COTE D IVOIRE</t>
+  </si>
+  <si>
+    <t>2722507830</t>
+  </si>
+  <si>
+    <t>STE FLASH VEHICLES</t>
+  </si>
+  <si>
+    <t>BUVPN160156</t>
+  </si>
+  <si>
+    <t>STE BANQUE REGIONALE DE MARCHES COTE D IVOIRE</t>
+  </si>
+  <si>
+    <t>2721750600</t>
+  </si>
+  <si>
+    <t>STE SPIRAL SARL</t>
+  </si>
+  <si>
     <t>20/05/2026</t>
   </si>
   <si>
+    <t>BUVPN170285</t>
+  </si>
+  <si>
     <t>BOLLORE</t>
   </si>
   <si>
+    <t>SYTHD190019</t>
+  </si>
+  <si>
     <t>LOTERIE NATIONALE DE CI LONACI</t>
   </si>
   <si>
+    <t>BUVPN220151</t>
+  </si>
+  <si>
+    <t>NSIA</t>
+  </si>
+  <si>
+    <t>BUVPN150085</t>
+  </si>
+  <si>
+    <t>BOA</t>
+  </si>
+  <si>
+    <t>VPNLL050192</t>
+  </si>
+  <si>
     <t>DOUANES</t>
   </si>
   <si>
+    <t>2721233000</t>
+  </si>
+  <si>
+    <t>GROUPEMENT DES SERVICES EAU ET ELECTRICITE CIE SODECI ET GS2E</t>
+  </si>
+  <si>
+    <t>BUVPN230216</t>
+  </si>
+  <si>
+    <t>SYTHD160040</t>
+  </si>
+  <si>
+    <t>STE MEDLOG</t>
+  </si>
+  <si>
+    <t>VPNLL060010</t>
+  </si>
+  <si>
+    <t>SYTHD180074</t>
+  </si>
+  <si>
+    <t>STE BERNABE CI KM4</t>
+  </si>
+  <si>
+    <t>2721235900</t>
+  </si>
+  <si>
+    <t>STE CMA CGM COTE D IVOIRE</t>
+  </si>
+  <si>
+    <t>2721750900</t>
+  </si>
+  <si>
+    <t>STE CROWN SIEM</t>
+  </si>
+  <si>
+    <t>2721239200</t>
+  </si>
+  <si>
+    <t>BUVPN220122</t>
+  </si>
+  <si>
+    <t>2721355723</t>
+  </si>
+  <si>
+    <t>ORG CENTRE NATIONAL DE TRANSFUSION SANGUINE</t>
+  </si>
+  <si>
+    <t>2722598310</t>
+  </si>
+  <si>
+    <t>MIN MINISTERE DE LA FAMILLE</t>
+  </si>
+  <si>
+    <t>17/02/2026</t>
+  </si>
+  <si>
+    <t>2722228640</t>
+  </si>
+  <si>
+    <t>STE REGUS PLEIN CIEL BUSINESS CENTER</t>
+  </si>
+  <si>
     <t>18/02/2026</t>
   </si>
   <si>
+    <t>2722509600</t>
+  </si>
+  <si>
+    <t>ASSOC MUPEMENET CI</t>
+  </si>
+  <si>
+    <t>BUVPN210191</t>
+  </si>
+  <si>
     <t>TRESOR</t>
   </si>
   <si>
+    <t>BUVPN240030</t>
+  </si>
+  <si>
+    <t>STE ASSUREURS CONSEILS COTE D IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD200196</t>
+  </si>
+  <si>
+    <t>STE GRANT THORNTON AUDIT COTE D IVOIRE SAS</t>
+  </si>
+  <si>
+    <t>2722417110</t>
+  </si>
+  <si>
+    <t>STE COMPAGNIE AFRICAINE DE CREDIT</t>
+  </si>
+  <si>
+    <t>SYTHD240333</t>
+  </si>
+  <si>
+    <t>VPNLL110030</t>
+  </si>
+  <si>
+    <t>ETS BANQUE SAHELO SAHARIENNE POUR L INVESTISSEMENT ET LE COMMERCE EN COTE D IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD120066</t>
+  </si>
+  <si>
+    <t>STE SOCIETE DE TRANSPORT ABIDJANAIS</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
+    <t>BUVPN190213</t>
+  </si>
+  <si>
+    <t>BUVPN210064</t>
+  </si>
+  <si>
+    <t>2721757100</t>
+  </si>
+  <si>
+    <t>2721221895</t>
+  </si>
+  <si>
+    <t>STE SOCIETE INTERNATIONALE DE LOGSTIQUE SHIPPING</t>
+  </si>
+  <si>
+    <t>22/02/2026</t>
+  </si>
+  <si>
+    <t>BUVPN200057</t>
+  </si>
+  <si>
+    <t>STE NATIONALE D OPERATION PETROLIERES DE COTE D IVOIRE</t>
+  </si>
+  <si>
+    <t>2721283888</t>
+  </si>
+  <si>
+    <t>STE TEDIS PHARMA COTE D IVOIRE</t>
+  </si>
+  <si>
+    <t>2721220400</t>
+  </si>
+  <si>
+    <t>BUVPN230241</t>
+  </si>
+  <si>
+    <t>STE AFRICA GLOBAL LOGISTICS</t>
+  </si>
+  <si>
+    <t>VPNLL070046</t>
+  </si>
+  <si>
+    <t>VPNLL060188</t>
+  </si>
+  <si>
+    <t>SYTHD230263</t>
+  </si>
+  <si>
+    <t>STE ROMEU</t>
+  </si>
+  <si>
+    <t>2721599555</t>
+  </si>
+  <si>
+    <t>STE KOIRA MULTI INDUSTRIES</t>
+  </si>
+  <si>
+    <t>SYTHD250223</t>
+  </si>
+  <si>
+    <t>SIFCOM</t>
+  </si>
+  <si>
+    <t>BUVPN200094</t>
+  </si>
+  <si>
+    <t>BUVPN200080</t>
+  </si>
+  <si>
     <t>STE CORIS BANK INTERNATIONAL</t>
   </si>
   <si>
+    <t>SYTHD110016</t>
+  </si>
+  <si>
+    <t>STE SIFCOM</t>
+  </si>
+  <si>
+    <t>BUVPN230234</t>
+  </si>
+  <si>
+    <t>2721245007</t>
+  </si>
+  <si>
+    <t>CHAMBRE DE COMMERCE ET D INDUSTRIE DE COTE D IVOIRE D IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD230205</t>
+  </si>
+  <si>
+    <t>ETS CHAMBRE DE COMMERCE ET D INDUSTRIE DE COTE D IVOIRE D IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD240155</t>
+  </si>
+  <si>
+    <t>STE ORANGE COTE D IVOIRE S A</t>
+  </si>
+  <si>
+    <t>BUVPN150580</t>
+  </si>
+  <si>
+    <t>BUVPN180031</t>
+  </si>
+  <si>
+    <t>BUVPN230068</t>
+  </si>
+  <si>
+    <t>VPNLL060013</t>
+  </si>
+  <si>
+    <t>2721755835</t>
+  </si>
+  <si>
+    <t>BUVPN220259</t>
+  </si>
+  <si>
+    <t>2720255050</t>
+  </si>
+  <si>
+    <t>STE CYRIAN INTERNATIONAL</t>
+  </si>
+  <si>
     <t>06/03/2026</t>
   </si>
   <si>
+    <t>2720278880</t>
+  </si>
+  <si>
+    <t>MAJORIS FINANCIAL GROUP</t>
+  </si>
+  <si>
+    <t>2720307650</t>
+  </si>
+  <si>
+    <t>COMPAGNIE IVOIRIENNE DE PRODUCTION D ELECTRICITE</t>
+  </si>
+  <si>
+    <t>BUVPN220261</t>
+  </si>
+  <si>
+    <t>STE CITIBANK COTE D IVOIRE SA</t>
+  </si>
+  <si>
+    <t>2720229418</t>
+  </si>
+  <si>
+    <t>ETS CABINET DE MAITRE ZEHOURI</t>
+  </si>
+  <si>
+    <t>SYTHD240290</t>
+  </si>
+  <si>
+    <t>STE SEALOGIS PROJETS COTE D IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD230229</t>
+  </si>
+  <si>
+    <t>STE DEPOSITAIRE CENTRAL BANQUE DE REGLEMENT</t>
+  </si>
+  <si>
+    <t>2720332960</t>
+  </si>
+  <si>
+    <t>SYTHD250248</t>
+  </si>
+  <si>
+    <t>SOCIETE DE COMMERCIALISATION DE CAFE CACAO</t>
+  </si>
+  <si>
     <t>14/05/2026</t>
   </si>
   <si>
+    <t>2721221838</t>
+  </si>
+  <si>
+    <t>STE COLIMEX IVORY</t>
+  </si>
+  <si>
+    <t>SYTHD240087</t>
+  </si>
+  <si>
+    <t>STE ALTERA INFRASTRUCTURE VOYAGEUR AS</t>
+  </si>
+  <si>
+    <t>BUVPN250038</t>
+  </si>
+  <si>
     <t>SIB</t>
   </si>
   <si>
+    <t>BUVPN180045</t>
+  </si>
+  <si>
+    <t>2721258305</t>
+  </si>
+  <si>
+    <t>STE RADIODIFFUSION TELEVISION IVOIRIENNE</t>
+  </si>
+  <si>
+    <t>2721756925</t>
+  </si>
+  <si>
+    <t>STE OCEAN NETWORK EXPRESS IVOIRY COAST</t>
+  </si>
+  <si>
+    <t>2721358883</t>
+  </si>
+  <si>
+    <t>STE TRANSIT CENTER</t>
+  </si>
+  <si>
+    <t>VPNLL110089</t>
+  </si>
+  <si>
+    <t>2721222221</t>
+  </si>
+  <si>
+    <t>STE SOGENA COTE D IVOIRE</t>
+  </si>
+  <si>
+    <t>BUVPN230256</t>
+  </si>
+  <si>
+    <t>13/11/2025</t>
+  </si>
+  <si>
+    <t>2721212250</t>
+  </si>
+  <si>
+    <t>STE GRAPHICOLOR</t>
+  </si>
+  <si>
+    <t>BUVPN220282</t>
+  </si>
+  <si>
+    <t>2721216370</t>
+  </si>
+  <si>
+    <t>TECTRA</t>
+  </si>
+  <si>
+    <t>SYTHD140199</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>2721751480</t>
+  </si>
+  <si>
+    <t>STE GRAFICA IVOIRE</t>
+  </si>
+  <si>
+    <t>2721223232</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIRIENNE DE PROMOTION DE SUPERMARCHES</t>
+  </si>
+  <si>
+    <t>BUVPN170101</t>
+  </si>
+  <si>
     <t>DGI</t>
   </si>
   <si>
+    <t>VPNLL060048</t>
+  </si>
+  <si>
+    <t>BUVPN230214</t>
+  </si>
+  <si>
+    <t>2721251587</t>
+  </si>
+  <si>
     <t>STE GMT SHIPPING CI SA</t>
   </si>
   <si>
+    <t>SYTHD250014</t>
+  </si>
+  <si>
+    <t>LE CLIENT STE UNITED CAPITAL ASSET MANAGEMENT WEST AFRICA LIMITED</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>SYTHD230248</t>
+  </si>
+  <si>
+    <t>STE TRIDEM PHARMA AFRIQUE FRANCOPHONE</t>
+  </si>
+  <si>
+    <t>2722228910</t>
+  </si>
+  <si>
+    <t>STE UNITED CAPITAL ASSET MANAGEMENT WEST AFRICA LIMITED</t>
+  </si>
+  <si>
+    <t>2723536464</t>
+  </si>
+  <si>
+    <t>STE INDUSTRIELLE DE PRODUITS PLASTIQUES ET CHIMIQUES</t>
+  </si>
+  <si>
     <t>12/04/2025</t>
+  </si>
+  <si>
+    <t>BUVPN240168</t>
   </si>
   <si>
     <t>STE BGFIBANK</t>
@@ -1196,7 +1706,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1221,6 +1731,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1535,7 +2048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C186"/>
+  <dimension ref="A1:C286"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="1"/>
@@ -1551,2053 +2064,3153 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>364</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>96</v>
+        <v>80</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="C43" s="10">
+        <v>45989</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>12</v>
+        <v>91</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>3</v>
+        <v>137</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>365</v>
+        <v>140</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>54</v>
+        <v>147</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>183</v>
+        <v>164</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>8</v>
+        <v>166</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>183</v>
+        <v>172</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>190</v>
+        <v>45</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>5</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>214</v>
+        <v>45</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>5</v>
+        <v>141</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>5</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>5</v>
+        <v>210</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>5</v>
+        <v>213</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>4</v>
+        <v>215</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>13</v>
+        <v>213</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>13</v>
+        <v>213</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>13</v>
+        <v>213</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>13</v>
+        <v>213</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>233</v>
+        <v>45</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>243</v>
+        <v>45</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>160</v>
+        <v>243</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>261</v>
+        <v>39</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>8</v>
+        <v>261</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>149</v>
+        <v>265</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>8</v>
+        <v>268</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>5</v>
+        <v>266</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>5</v>
+        <v>266</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>5</v>
+        <v>266</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>285</v>
+        <v>125</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>285</v>
+        <v>125</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>285</v>
+        <v>125</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>285</v>
+        <v>125</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>285</v>
+        <v>125</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>295</v>
+        <v>125</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>297</v>
+        <v>71</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>298</v>
+        <v>125</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>300</v>
+        <v>71</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>255</v>
+        <v>125</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>255</v>
+        <v>125</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>304</v>
+        <v>71</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>255</v>
+        <v>125</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>307</v>
+        <v>125</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>102</v>
+        <v>301</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>183</v>
+        <v>302</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>11</v>
+        <v>304</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>5</v>
+        <v>310</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>327</v>
+        <v>176</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>5</v>
+        <v>310</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>40</v>
+        <v>310</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C176" s="9" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="B180" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="C168" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="2" t="s">
+      <c r="B181" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="C181" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="C169" s="3">
+      <c r="B182" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C189" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C269" s="3">
         <v>45992</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C170" s="3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C270" s="3">
         <v>45994</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C171" s="3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C271" s="3">
         <v>45996</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A172" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="C172" s="3">
+    <row r="272" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C272" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C173" s="3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C273" s="3">
         <v>46007</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C174" s="3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C274" s="3">
         <v>46008</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C175" s="3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C275" s="3">
         <v>46008</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A176" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="C176" s="3">
+    <row r="276" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C276" s="3">
         <v>46008</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A177" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="C177" s="3">
+    <row r="277" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C277" s="3">
         <v>46010</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A178" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="B178" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C178" s="3">
+    <row r="278" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C278" s="3">
         <v>46032</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C179" s="7">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C279" s="7">
         <v>46091</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A180" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B180" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="C180" s="3">
+    <row r="280" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A280" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C280" s="3">
         <v>46099</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C181" s="3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C281" s="3">
         <v>46115</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="6">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="6">
         <v>2721247429</v>
       </c>
-      <c r="B182" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="C182" s="7">
+      <c r="B282" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="C282" s="7">
         <v>46139</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="6">
         <v>2721255054</v>
       </c>
-      <c r="B183" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="C183" s="7">
+      <c r="B283" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="C283" s="7">
         <v>46139</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="6">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="6">
         <v>2721273128</v>
       </c>
-      <c r="B184" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="C184" s="7">
+      <c r="B284" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="C284" s="7">
         <v>46139</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="6">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="6">
         <v>2721219191</v>
       </c>
-      <c r="B185" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="C185" s="7">
+      <c r="B285" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="C285" s="7">
         <v>46147</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="C186" s="8" t="s">
-        <v>363</v>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="C286" s="8" t="s">
+        <v>533</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C186"/>
-  <conditionalFormatting sqref="A183:A186 A169:A180">
+  <autoFilter ref="A1:C286"/>
+  <conditionalFormatting sqref="A283:A286 A269:A280">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A181:A182">
+  <conditionalFormatting sqref="A281:A282">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reference.xlsx
+++ b/reference.xlsx
@@ -1631,10 +1631,10 @@
     <t>26/03/026</t>
   </si>
   <si>
-    <t>Datede correction</t>
-  </si>
-  <si>
     <t>03/06/2026</t>
+  </si>
+  <si>
+    <t>Date de correction</t>
   </si>
 </sst>
 </file>
@@ -2064,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -3989,7 +3989,7 @@
         <v>330</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">

--- a/reference.xlsx
+++ b/reference.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JGMZ9014\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MBKZ6901\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6495"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20496" windowHeight="6492"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="536">
   <si>
     <t>ND</t>
   </si>
@@ -1631,10 +1631,10 @@
     <t>26/03/026</t>
   </si>
   <si>
+    <t>Datede correction</t>
+  </si>
+  <si>
     <t>03/06/2026</t>
-  </si>
-  <si>
-    <t>Date de correction</t>
   </si>
 </sst>
 </file>
@@ -2049,14 +2049,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C286"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.5546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="1"/>
+    <col min="4" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2064,10 +2065,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -2078,7 +2079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -2089,7 +2090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2100,7 +2101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
@@ -2111,7 +2112,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -2122,7 +2123,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -2133,7 +2134,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
@@ -2144,7 +2145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
@@ -2155,7 +2156,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
@@ -2166,7 +2167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
@@ -2177,7 +2178,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>25</v>
       </c>
@@ -2188,7 +2189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>27</v>
       </c>
@@ -2199,7 +2200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>29</v>
       </c>
@@ -2210,7 +2211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>31</v>
       </c>
@@ -2221,7 +2222,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>33</v>
       </c>
@@ -2232,7 +2233,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>36</v>
       </c>
@@ -2243,7 +2244,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
@@ -2254,7 +2255,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
@@ -2265,7 +2266,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>42</v>
       </c>
@@ -2276,7 +2277,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>44</v>
       </c>
@@ -2287,7 +2288,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>46</v>
       </c>
@@ -2298,7 +2299,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>48</v>
       </c>
@@ -2309,7 +2310,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>49</v>
       </c>
@@ -2320,7 +2321,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>51</v>
       </c>
@@ -2331,7 +2332,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>52</v>
       </c>
@@ -2342,7 +2343,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>54</v>
       </c>
@@ -2353,7 +2354,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>56</v>
       </c>
@@ -2364,7 +2365,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>58</v>
       </c>
@@ -2375,7 +2376,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>59</v>
       </c>
@@ -2386,7 +2387,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>60</v>
       </c>
@@ -2397,7 +2398,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>62</v>
       </c>
@@ -2408,7 +2409,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>65</v>
       </c>
@@ -2419,7 +2420,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>68</v>
       </c>
@@ -2430,7 +2431,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>70</v>
       </c>
@@ -2441,7 +2442,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>72</v>
       </c>
@@ -2452,7 +2453,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>74</v>
       </c>
@@ -2463,7 +2464,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>76</v>
       </c>
@@ -2474,7 +2475,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>78</v>
       </c>
@@ -2485,7 +2486,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>79</v>
       </c>
@@ -2496,7 +2497,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>81</v>
       </c>
@@ -2507,7 +2508,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>84</v>
       </c>
@@ -2518,7 +2519,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>85</v>
       </c>
@@ -2529,7 +2530,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>86</v>
       </c>
@@ -2540,7 +2541,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>87</v>
       </c>
@@ -2551,7 +2552,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>90</v>
       </c>
@@ -2562,7 +2563,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>92</v>
       </c>
@@ -2573,7 +2574,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>94</v>
       </c>
@@ -2584,7 +2585,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>95</v>
       </c>
@@ -2595,7 +2596,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>97</v>
       </c>
@@ -2606,7 +2607,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>98</v>
       </c>
@@ -2617,7 +2618,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>99</v>
       </c>
@@ -2628,7 +2629,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>101</v>
       </c>
@@ -2639,7 +2640,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>103</v>
       </c>
@@ -2650,7 +2651,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>105</v>
       </c>
@@ -2661,7 +2662,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>106</v>
       </c>
@@ -2672,7 +2673,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>108</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>110</v>
       </c>
@@ -2694,7 +2695,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>111</v>
       </c>
@@ -2705,7 +2706,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>113</v>
       </c>
@@ -2716,7 +2717,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>115</v>
       </c>
@@ -2727,7 +2728,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>117</v>
       </c>
@@ -2738,7 +2739,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>118</v>
       </c>
@@ -2749,7 +2750,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>119</v>
       </c>
@@ -2760,7 +2761,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>120</v>
       </c>
@@ -2771,7 +2772,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>121</v>
       </c>
@@ -2782,7 +2783,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>122</v>
       </c>
@@ -2793,7 +2794,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>123</v>
       </c>
@@ -2804,7 +2805,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>126</v>
       </c>
@@ -2815,7 +2816,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>128</v>
       </c>
@@ -2826,7 +2827,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>130</v>
       </c>
@@ -2837,7 +2838,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>132</v>
       </c>
@@ -2848,7 +2849,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>134</v>
       </c>
@@ -2859,7 +2860,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>136</v>
       </c>
@@ -2870,7 +2871,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>138</v>
       </c>
@@ -2881,7 +2882,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>139</v>
       </c>
@@ -2892,7 +2893,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>142</v>
       </c>
@@ -2903,7 +2904,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>144</v>
       </c>
@@ -2914,7 +2915,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>146</v>
       </c>
@@ -2925,7 +2926,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>148</v>
       </c>
@@ -2936,7 +2937,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>149</v>
       </c>
@@ -2947,7 +2948,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>151</v>
       </c>
@@ -2958,7 +2959,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>153</v>
       </c>
@@ -2969,7 +2970,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>155</v>
       </c>
@@ -2980,7 +2981,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>156</v>
       </c>
@@ -2991,7 +2992,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>158</v>
       </c>
@@ -3002,7 +3003,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>160</v>
       </c>
@@ -3013,7 +3014,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>162</v>
       </c>
@@ -3024,7 +3025,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>163</v>
       </c>
@@ -3035,7 +3036,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>165</v>
       </c>
@@ -3046,7 +3047,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>167</v>
       </c>
@@ -3057,7 +3058,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>169</v>
       </c>
@@ -3068,7 +3069,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>171</v>
       </c>
@@ -3079,7 +3080,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>173</v>
       </c>
@@ -3090,7 +3091,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>174</v>
       </c>
@@ -3101,7 +3102,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>175</v>
       </c>
@@ -3112,7 +3113,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>177</v>
       </c>
@@ -3123,7 +3124,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>180</v>
       </c>
@@ -3134,7 +3135,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>182</v>
       </c>
@@ -3145,7 +3146,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>184</v>
       </c>
@@ -3156,7 +3157,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>187</v>
       </c>
@@ -3167,7 +3168,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>189</v>
       </c>
@@ -3178,7 +3179,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>191</v>
       </c>
@@ -3189,7 +3190,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>193</v>
       </c>
@@ -3200,7 +3201,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>195</v>
       </c>
@@ -3211,7 +3212,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>197</v>
       </c>
@@ -3222,7 +3223,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>199</v>
       </c>
@@ -3233,7 +3234,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>201</v>
       </c>
@@ -3244,7 +3245,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>202</v>
       </c>
@@ -3255,7 +3256,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>204</v>
       </c>
@@ -3266,7 +3267,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>206</v>
       </c>
@@ -3277,7 +3278,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>208</v>
       </c>
@@ -3288,7 +3289,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>211</v>
       </c>
@@ -3299,7 +3300,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>214</v>
       </c>
@@ -3310,7 +3311,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>216</v>
       </c>
@@ -3321,7 +3322,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>218</v>
       </c>
@@ -3332,7 +3333,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>220</v>
       </c>
@@ -3343,7 +3344,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>222</v>
       </c>
@@ -3354,7 +3355,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>223</v>
       </c>
@@ -3365,7 +3366,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>225</v>
       </c>
@@ -3376,7 +3377,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>227</v>
       </c>
@@ -3387,7 +3388,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>229</v>
       </c>
@@ -3398,7 +3399,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>231</v>
       </c>
@@ -3409,7 +3410,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>232</v>
       </c>
@@ -3420,7 +3421,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>234</v>
       </c>
@@ -3431,7 +3432,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>236</v>
       </c>
@@ -3442,7 +3443,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>238</v>
       </c>
@@ -3453,7 +3454,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>240</v>
       </c>
@@ -3464,7 +3465,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>242</v>
       </c>
@@ -3475,7 +3476,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>244</v>
       </c>
@@ -3486,7 +3487,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>246</v>
       </c>
@@ -3497,7 +3498,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>249</v>
       </c>
@@ -3508,7 +3509,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>250</v>
       </c>
@@ -3519,7 +3520,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>252</v>
       </c>
@@ -3530,7 +3531,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>254</v>
       </c>
@@ -3541,7 +3542,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>256</v>
       </c>
@@ -3552,7 +3553,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>259</v>
       </c>
@@ -3563,7 +3564,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>260</v>
       </c>
@@ -3574,7 +3575,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>262</v>
       </c>
@@ -3585,7 +3586,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>264</v>
       </c>
@@ -3596,7 +3597,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>267</v>
       </c>
@@ -3607,7 +3608,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>269</v>
       </c>
@@ -3618,7 +3619,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>271</v>
       </c>
@@ -3629,7 +3630,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>273</v>
       </c>
@@ -3640,7 +3641,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>275</v>
       </c>
@@ -3651,7 +3652,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>276</v>
       </c>
@@ -3662,7 +3663,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
         <v>278</v>
       </c>
@@ -3673,7 +3674,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>280</v>
       </c>
@@ -3684,7 +3685,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>282</v>
       </c>
@@ -3695,7 +3696,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>284</v>
       </c>
@@ -3706,7 +3707,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>285</v>
       </c>
@@ -3717,7 +3718,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
         <v>286</v>
       </c>
@@ -3728,7 +3729,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
         <v>288</v>
       </c>
@@ -3739,7 +3740,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>289</v>
       </c>
@@ -3750,7 +3751,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
         <v>291</v>
       </c>
@@ -3761,7 +3762,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
         <v>294</v>
       </c>
@@ -3772,7 +3773,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
         <v>296</v>
       </c>
@@ -3783,7 +3784,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>298</v>
       </c>
@@ -3794,7 +3795,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>300</v>
       </c>
@@ -3805,7 +3806,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>303</v>
       </c>
@@ -3816,7 +3817,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
         <v>305</v>
       </c>
@@ -3827,7 +3828,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
         <v>307</v>
       </c>
@@ -3838,7 +3839,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
         <v>309</v>
       </c>
@@ -3849,7 +3850,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
         <v>311</v>
       </c>
@@ -3860,7 +3861,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>312</v>
       </c>
@@ -3871,7 +3872,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
         <v>314</v>
       </c>
@@ -3882,7 +3883,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
         <v>315</v>
       </c>
@@ -3893,7 +3894,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="5" t="s">
         <v>316</v>
       </c>
@@ -3904,7 +3905,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="5" t="s">
         <v>318</v>
       </c>
@@ -3915,7 +3916,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="5" t="s">
         <v>320</v>
       </c>
@@ -3926,7 +3927,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="5" t="s">
         <v>322</v>
       </c>
@@ -3937,7 +3938,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="5" t="s">
         <v>323</v>
       </c>
@@ -3948,7 +3949,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="5" t="s">
         <v>324</v>
       </c>
@@ -3959,7 +3960,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="5" t="s">
         <v>326</v>
       </c>
@@ -3970,7 +3971,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="5" t="s">
         <v>327</v>
       </c>
@@ -3981,7 +3982,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="5" t="s">
         <v>329</v>
       </c>
@@ -3989,10 +3990,10 @@
         <v>330</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="5" t="s">
         <v>331</v>
       </c>
@@ -4003,7 +4004,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="5" t="s">
         <v>332</v>
       </c>
@@ -4014,7 +4015,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="5" t="s">
         <v>333</v>
       </c>
@@ -4025,7 +4026,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>334</v>
       </c>
@@ -4036,7 +4037,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
         <v>335</v>
       </c>
@@ -4047,7 +4048,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>337</v>
       </c>
@@ -4058,7 +4059,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>340</v>
       </c>
@@ -4069,7 +4070,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
         <v>342</v>
       </c>
@@ -4080,7 +4081,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
         <v>344</v>
       </c>
@@ -4091,7 +4092,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="5" t="s">
         <v>346</v>
       </c>
@@ -4102,7 +4103,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="5" t="s">
         <v>348</v>
       </c>
@@ -4113,7 +4114,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="5" t="s">
         <v>350</v>
       </c>
@@ -4124,7 +4125,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="5" t="s">
         <v>351</v>
       </c>
@@ -4135,7 +4136,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="5" t="s">
         <v>352</v>
       </c>
@@ -4146,7 +4147,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="5" t="s">
         <v>354</v>
       </c>
@@ -4157,7 +4158,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="5" t="s">
         <v>355</v>
       </c>
@@ -4168,7 +4169,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="5" t="s">
         <v>357</v>
       </c>
@@ -4179,7 +4180,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="5" t="s">
         <v>359</v>
       </c>
@@ -4190,7 +4191,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" s="5" t="s">
         <v>362</v>
       </c>
@@ -4201,7 +4202,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="5" t="s">
         <v>363</v>
       </c>
@@ -4212,7 +4213,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" s="5" t="s">
         <v>365</v>
       </c>
@@ -4223,7 +4224,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="5" t="s">
         <v>366</v>
       </c>
@@ -4234,7 +4235,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" s="5" t="s">
         <v>369</v>
       </c>
@@ -4245,7 +4246,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" s="5" t="s">
         <v>370</v>
       </c>
@@ -4256,7 +4257,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" s="5" t="s">
         <v>371</v>
       </c>
@@ -4267,7 +4268,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" s="5" t="s">
         <v>373</v>
       </c>
@@ -4278,7 +4279,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" s="5" t="s">
         <v>374</v>
       </c>
@@ -4289,7 +4290,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" s="5" t="s">
         <v>376</v>
       </c>
@@ -4300,7 +4301,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
         <v>378</v>
       </c>
@@ -4311,7 +4312,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" s="5" t="s">
         <v>380</v>
       </c>
@@ -4322,7 +4323,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" s="5" t="s">
         <v>382</v>
       </c>
@@ -4333,7 +4334,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" s="5" t="s">
         <v>383</v>
       </c>
@@ -4344,7 +4345,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="5" t="s">
         <v>385</v>
       </c>
@@ -4355,7 +4356,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="5" t="s">
         <v>387</v>
       </c>
@@ -4366,7 +4367,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
         <v>389</v>
       </c>
@@ -4377,7 +4378,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
         <v>391</v>
       </c>
@@ -4388,7 +4389,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
         <v>393</v>
       </c>
@@ -4399,7 +4400,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="5" t="s">
         <v>395</v>
       </c>
@@ -4410,7 +4411,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="5" t="s">
         <v>396</v>
       </c>
@@ -4421,7 +4422,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="5" t="s">
         <v>398</v>
       </c>
@@ -4432,7 +4433,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="5" t="s">
         <v>400</v>
       </c>
@@ -4443,7 +4444,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="5" t="s">
         <v>402</v>
       </c>
@@ -4454,7 +4455,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="5" t="s">
         <v>404</v>
       </c>
@@ -4465,7 +4466,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="5" t="s">
         <v>406</v>
       </c>
@@ -4476,7 +4477,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="5" t="s">
         <v>408</v>
       </c>
@@ -4487,7 +4488,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="5" t="s">
         <v>410</v>
       </c>
@@ -4498,7 +4499,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="5" t="s">
         <v>412</v>
       </c>
@@ -4509,7 +4510,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="5" t="s">
         <v>414</v>
       </c>
@@ -4520,7 +4521,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" s="5" t="s">
         <v>417</v>
       </c>
@@ -4531,7 +4532,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" s="5" t="s">
         <v>418</v>
       </c>
@@ -4542,7 +4543,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" s="5" t="s">
         <v>420</v>
       </c>
@@ -4553,7 +4554,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" s="5" t="s">
         <v>422</v>
       </c>
@@ -4564,7 +4565,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>424</v>
       </c>
@@ -4575,7 +4576,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>426</v>
       </c>
@@ -4586,7 +4587,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
         <v>428</v>
       </c>
@@ -4597,7 +4598,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" s="5" t="s">
         <v>430</v>
       </c>
@@ -4608,7 +4609,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" s="5" t="s">
         <v>433</v>
       </c>
@@ -4619,7 +4620,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" s="5" t="s">
         <v>435</v>
       </c>
@@ -4630,7 +4631,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="5" t="s">
         <v>437</v>
       </c>
@@ -4641,7 +4642,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="5" t="s">
         <v>438</v>
       </c>
@@ -4652,7 +4653,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" s="5" t="s">
         <v>440</v>
       </c>
@@ -4663,7 +4664,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="5" t="s">
         <v>441</v>
       </c>
@@ -4674,7 +4675,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" s="5" t="s">
         <v>443</v>
       </c>
@@ -4685,7 +4686,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" s="5" t="s">
         <v>446</v>
       </c>
@@ -4696,7 +4697,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" s="5" t="s">
         <v>448</v>
       </c>
@@ -4707,7 +4708,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" s="5" t="s">
         <v>449</v>
       </c>
@@ -4718,7 +4719,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" s="5" t="s">
         <v>451</v>
       </c>
@@ -4729,18 +4730,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" s="5" t="s">
         <v>453</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="C244" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C244" s="7">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" s="5" t="s">
         <v>456</v>
       </c>
@@ -4751,7 +4752,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" s="5" t="s">
         <v>457</v>
       </c>
@@ -4762,7 +4763,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" s="5" t="s">
         <v>459</v>
       </c>
@@ -4773,7 +4774,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" s="5" t="s">
         <v>461</v>
       </c>
@@ -4784,7 +4785,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" s="5" t="s">
         <v>463</v>
       </c>
@@ -4795,7 +4796,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" s="5" t="s">
         <v>466</v>
       </c>
@@ -4806,7 +4807,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" s="5" t="s">
         <v>469</v>
       </c>
@@ -4817,7 +4818,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" s="5" t="s">
         <v>471</v>
       </c>
@@ -4828,7 +4829,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" s="5" t="s">
         <v>473</v>
       </c>
@@ -4839,7 +4840,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" s="5" t="s">
         <v>475</v>
       </c>
@@ -4850,7 +4851,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" s="5" t="s">
         <v>478</v>
       </c>
@@ -4861,7 +4862,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" s="5" t="s">
         <v>480</v>
       </c>
@@ -4872,7 +4873,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" s="5" t="s">
         <v>482</v>
       </c>
@@ -4883,7 +4884,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" s="5" t="s">
         <v>484</v>
       </c>
@@ -4894,7 +4895,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" s="5" t="s">
         <v>487</v>
       </c>
@@ -4905,7 +4906,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" s="5" t="s">
         <v>488</v>
       </c>
@@ -4916,7 +4917,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" s="5" t="s">
         <v>490</v>
       </c>
@@ -4927,7 +4928,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" s="5" t="s">
         <v>493</v>
       </c>
@@ -4938,7 +4939,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" s="5" t="s">
         <v>495</v>
       </c>
@@ -4949,7 +4950,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" s="5" t="s">
         <v>496</v>
       </c>
@@ -4960,7 +4961,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" s="5" t="s">
         <v>498</v>
       </c>
@@ -4971,7 +4972,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" s="5" t="s">
         <v>501</v>
       </c>
@@ -4982,7 +4983,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" s="5" t="s">
         <v>503</v>
       </c>
@@ -4993,7 +4994,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" s="5" t="s">
         <v>504</v>
       </c>
@@ -5004,7 +5005,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>506</v>
       </c>
@@ -5015,7 +5016,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>508</v>
       </c>
@@ -5026,7 +5027,7 @@
         <v>45994</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>510</v>
       </c>
@@ -5037,7 +5038,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>511</v>
       </c>
@@ -5048,7 +5049,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>512</v>
       </c>
@@ -5059,7 +5060,7 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>514</v>
       </c>
@@ -5070,7 +5071,7 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>516</v>
       </c>
@@ -5081,7 +5082,7 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" ht="72" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>518</v>
       </c>
@@ -5092,7 +5093,7 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>519</v>
       </c>
@@ -5103,7 +5104,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>521</v>
       </c>
@@ -5114,7 +5115,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
         <v>522</v>
       </c>
@@ -5125,7 +5126,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>523</v>
       </c>
@@ -5136,7 +5137,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>525</v>
       </c>
@@ -5147,7 +5148,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
         <v>2721247429</v>
       </c>
@@ -5158,7 +5159,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
         <v>2721255054</v>
       </c>
@@ -5169,7 +5170,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
         <v>2721273128</v>
       </c>
@@ -5180,7 +5181,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
         <v>2721219191</v>
       </c>
@@ -5191,7 +5192,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
         <v>531</v>
       </c>

--- a/reference.xlsx
+++ b/reference.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="536">
   <si>
     <t>ND</t>
   </si>
@@ -4738,7 +4738,7 @@
         <v>454</v>
       </c>
       <c r="C244" s="7">
-        <v>46166</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
@@ -4759,8 +4759,8 @@
       <c r="B246" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="C246" s="5" t="s">
-        <v>455</v>
+      <c r="C246" s="7">
+        <v>46152</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
@@ -5038,7 +5038,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>511</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>518</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>519</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>521</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>523</v>
       </c>
